--- a/artfynd/A 22400-2025 artfynd.xlsx
+++ b/artfynd/A 22400-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>65115334</v>
       </c>
       <c r="B2" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -726,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>657401.1457649034</v>
+        <v>657401</v>
       </c>
       <c r="R2" t="n">
-        <v>6617975.281300485</v>
+        <v>6617975</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -798,10 +793,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>75322936</v>
+        <v>65115321</v>
       </c>
       <c r="B3" t="n">
-        <v>99091</v>
+        <v>58129</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -809,37 +804,48 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>223621</v>
+        <v>102623</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Lullula arborea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>300 m O om Odinslund, Upl</t>
+          <t>Odenslund, Suckunge, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>657444</v>
+        <v>657401</v>
       </c>
       <c r="R3" t="n">
-        <v>6618075</v>
+        <v>6617975</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -863,17 +869,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1996-01-01</t>
+          <t>2017-04-25</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1996-12-31</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Upplandsfloran - detaljuppgifter.</t>
+          <t>2017-04-25</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,34 +896,25 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>ängskog, skogsstig</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mora Aronsson</t>
+          <t>Jan Franzén</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Svenson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Upplands Flora 2010</t>
-        </is>
-      </c>
+          <t>Jan Franzén</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>75323269</v>
       </c>
       <c r="B4" t="n">
-        <v>109749</v>
+        <v>109896</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,6 +1015,117 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr">
+        <is>
+          <t>Upplands Flora 2010</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>75322936</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99232</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>223621</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Skogsnattviol</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia subsp. latiflora</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>300 m O om Odinslund, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>657444</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6618075</v>
+      </c>
+      <c r="S5" t="n">
+        <v>100</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Odensala</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>1996-01-01</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>1996-12-31</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Upplandsfloran - detaljuppgifter.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>ängskog, skogsstig</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mora Aronsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anders Svenson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
         <is>
           <t>Upplands Flora 2010</t>
         </is>

--- a/artfynd/A 22400-2025 artfynd.xlsx
+++ b/artfynd/A 22400-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -790,6 +795,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65115334</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -908,6 +918,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65115321</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1019,6 +1034,11 @@
           <t>Upplands Flora 2010</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75323269</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1130,8 +1150,19 @@
           <t>Upplands Flora 2010</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75322936</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>